--- a/Files/2037/DraftPicks.xlsx
+++ b/Files/2037/DraftPicks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/40f61192ff96ff75/Documents/Git/MaddenDraftTool/Files/2037/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E576E028-64C5-46BE-B3D5-CD95DF63B5EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_4B57CF4F2364FF18F55B1250EA3161BA935D3789" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AE151F2-34C8-4C1E-B11E-F8F40B46E5B4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,13 +71,13 @@
     <t>00101101010010100000000000000000</t>
   </si>
   <si>
+    <t>00101101010010100000000000010110</t>
+  </si>
+  <si>
     <t>00101101010010100000000000011101</t>
   </si>
   <si>
     <t>00101101010010100000000000100010</t>
-  </si>
-  <si>
-    <t>00101101010010100000000000010110</t>
   </si>
   <si>
     <t>00101101010010100000000000000010</t>
@@ -95,7 +95,13 @@
     <t>00101101010010100000000000011100</t>
   </si>
   <si>
+    <t>00101101010010100000000000011001</t>
+  </si>
+  <si>
     <t>00101101010010100000000000100011</t>
+  </si>
+  <si>
+    <t>00101101010010100000000000010001</t>
   </si>
   <si>
     <t>00101101010010100000000000000100</t>
@@ -116,9 +122,6 @@
     <t>00101101010010100000000000011111</t>
   </si>
   <si>
-    <t>00101101010010100000000000011001</t>
-  </si>
-  <si>
     <t>00101101010010100000000000000001</t>
   </si>
   <si>
@@ -126,9 +129,6 @@
   </si>
   <si>
     <t>00101101010010100000000000011011</t>
-  </si>
-  <si>
-    <t>00101101010010100000000000010001</t>
   </si>
   <si>
     <t>00101101010010100000000000010111</t>
@@ -530,9 +530,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F707"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -552,7 +552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -572,7 +572,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -592,7 +592,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -612,7 +612,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -632,7 +632,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -652,7 +652,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -672,7 +672,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -712,7 +712,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -732,7 +732,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -752,7 +752,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -772,7 +772,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -792,15 +792,15 @@
         <v>159</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -812,15 +812,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -832,15 +832,15 @@
         <v>223</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -852,15 +852,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -872,15 +872,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -892,15 +892,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -912,15 +912,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -932,15 +932,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -952,15 +952,15 @@
         <v>173</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -972,7 +972,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -992,7 +992,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1186,13 +1186,13 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>97</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -1206,61 +1206,61 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34">
         <v>129</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F35">
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36">
         <v>193</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1272,15 +1272,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -1292,15 +1292,15 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1312,15 +1312,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -1332,15 +1332,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -1352,15 +1352,15 @@
         <v>143</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -1372,15 +1372,15 @@
         <v>174</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -1392,15 +1392,15 @@
         <v>207</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -1412,15 +1412,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1432,15 +1432,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -1452,15 +1452,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -1472,15 +1472,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -1492,15 +1492,15 @@
         <v>158</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1512,15 +1512,15 @@
         <v>190</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1532,15 +1532,15 @@
         <v>222</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>6</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -1552,12 +1552,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
@@ -1572,15 +1572,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -1592,15 +1592,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -1652,35 +1652,35 @@
         <v>182</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F57">
         <v>214</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -1692,15 +1692,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -1712,15 +1712,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>6</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -1732,15 +1732,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>6</v>
       </c>
       <c r="B61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -1752,15 +1752,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>6</v>
       </c>
       <c r="B62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -1772,15 +1772,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>6</v>
       </c>
       <c r="B63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -1792,15 +1792,15 @@
         <v>178</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>6</v>
       </c>
       <c r="B64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -1812,7 +1812,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -1952,15 +1952,15 @@
         <v>202</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>6</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -1972,15 +1972,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>6</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C73" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -1992,15 +1992,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>6</v>
       </c>
       <c r="B74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -2012,15 +2012,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>6</v>
       </c>
       <c r="B75" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -2032,15 +2032,15 @@
         <v>111</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>6</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2066,18 +2066,18 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F77">
         <v>175</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>6</v>
       </c>
       <c r="B78" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C78" t="s">
         <v>32</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F78">
         <v>207</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>9</v>
       </c>
       <c r="C83" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -2192,7 +2192,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>6</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>6</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>6</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>6</v>
       </c>
@@ -2432,15 +2432,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>6</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C96" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D96">
         <v>0</v>
@@ -2452,15 +2452,15 @@
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>6</v>
       </c>
       <c r="B97" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>6</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>6</v>
       </c>
@@ -2506,13 +2506,13 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F99">
         <v>219</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>6</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>6</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>6</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>6</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>6</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>6</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>6</v>
       </c>
@@ -2652,15 +2652,15 @@
         <v>218</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>6</v>
       </c>
       <c r="B107" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C107" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -2672,15 +2672,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>6</v>
       </c>
       <c r="B108" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C108" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -2692,15 +2692,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>6</v>
       </c>
       <c r="B109" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C109" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -2712,15 +2712,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>6</v>
       </c>
       <c r="B110" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -2732,15 +2732,15 @@
         <v>101</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>6</v>
       </c>
       <c r="B111" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C111" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -2752,15 +2752,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>6</v>
       </c>
       <c r="B112" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C112" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -2772,15 +2772,15 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>6</v>
       </c>
       <c r="B113" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C113" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -2792,7 +2792,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>6</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>6</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>31</v>
       </c>
       <c r="C115" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D115">
         <v>0</v>
@@ -2832,15 +2832,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>6</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C116" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D116">
         <v>0</v>
@@ -2852,7 +2852,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>6</v>
       </c>
@@ -2872,15 +2872,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>6</v>
       </c>
       <c r="B118" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C118" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>6</v>
       </c>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="E119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F119">
         <v>173</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>6</v>
       </c>
@@ -2920,27 +2920,27 @@
         <v>18</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D120">
         <v>0</v>
       </c>
       <c r="E120">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F120">
         <v>205</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>6</v>
       </c>
       <c r="B121" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -2952,15 +2952,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>6</v>
       </c>
       <c r="B122" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C122" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -2972,15 +2972,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>6</v>
       </c>
       <c r="B123" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C123" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -2992,15 +2992,15 @@
         <v>74</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>6</v>
       </c>
       <c r="B124" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C124" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -3012,15 +3012,15 @@
         <v>105</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>6</v>
       </c>
       <c r="B125" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C125" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -3032,15 +3032,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>6</v>
       </c>
       <c r="B126" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C126" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -3052,15 +3052,15 @@
         <v>167</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>6</v>
       </c>
       <c r="B127" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C127" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -3072,7 +3072,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>6</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>6</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>6</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>6</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>6</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>6</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>6</v>
       </c>
@@ -3212,15 +3212,15 @@
         <v>216</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>6</v>
       </c>
       <c r="B135" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C135" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -3232,15 +3232,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>6</v>
       </c>
       <c r="B136" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C136" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -3252,15 +3252,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>6</v>
       </c>
       <c r="B137" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C137" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -3272,15 +3272,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>6</v>
       </c>
       <c r="B138" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C138" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -3292,7 +3292,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>6</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>6</v>
       </c>
@@ -3346,13 +3346,13 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F141">
         <v>221</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>6</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>31</v>
       </c>
       <c r="C142" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -3372,7 +3372,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>6</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>6</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>6</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>6</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>6</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>6</v>
       </c>
@@ -3492,15 +3492,15 @@
         <v>203</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>6</v>
       </c>
       <c r="B149" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C149" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D149">
         <v>2</v>
@@ -3512,15 +3512,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>6</v>
       </c>
       <c r="B150" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C150" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -3532,15 +3532,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>6</v>
       </c>
       <c r="B151" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C151" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D151">
         <v>2</v>
@@ -3552,15 +3552,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>6</v>
       </c>
       <c r="B152" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C152" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D152">
         <v>2</v>
@@ -3572,15 +3572,15 @@
         <v>99</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C153" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D153">
         <v>2</v>
@@ -3592,15 +3592,15 @@
         <v>131</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C154" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D154">
         <v>2</v>
@@ -3612,15 +3612,15 @@
         <v>163</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>6</v>
       </c>
       <c r="B155" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C155" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D155">
         <v>2</v>
@@ -3632,15 +3632,15 @@
         <v>195</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>6</v>
       </c>
       <c r="B156" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C156" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -3652,7 +3652,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>6</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>6</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>6</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>6</v>
       </c>
@@ -3726,13 +3726,13 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F160">
         <v>136</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>6</v>
       </c>
@@ -3746,41 +3746,41 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F161">
         <v>168</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>6</v>
       </c>
       <c r="B162" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C162" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F162">
         <v>200</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>6</v>
       </c>
       <c r="B163" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C163" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -3792,15 +3792,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>6</v>
       </c>
       <c r="B164" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C164" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -3812,15 +3812,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>6</v>
       </c>
       <c r="B165" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C165" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -3832,15 +3832,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>6</v>
       </c>
       <c r="B166" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C166" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -3852,15 +3852,15 @@
         <v>96</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>6</v>
       </c>
       <c r="B167" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C167" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -3872,15 +3872,15 @@
         <v>128</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>6</v>
       </c>
       <c r="B168" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C168" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -3892,12 +3892,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>6</v>
       </c>
       <c r="B169" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C169" t="s">
         <v>14</v>
@@ -3912,7 +3912,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>6</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>6</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>6</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>6</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>6</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>6</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>6</v>
       </c>
@@ -4052,15 +4052,15 @@
         <v>211</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C177" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>6</v>
       </c>
@@ -4092,15 +4092,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>6</v>
       </c>
       <c r="B179" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C179" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -4112,7 +4112,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>6</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>31</v>
       </c>
       <c r="C180" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -4132,7 +4132,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>6</v>
       </c>
@@ -4152,27 +4152,27 @@
         <v>145</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>6</v>
       </c>
       <c r="B182" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C182" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D182">
         <v>0</v>
       </c>
       <c r="E182">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F182">
         <v>177</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>6</v>
       </c>
@@ -4186,21 +4186,21 @@
         <v>0</v>
       </c>
       <c r="E183">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F183">
         <v>209</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>6</v>
       </c>
       <c r="B184" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C184" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D184">
         <v>1</v>
@@ -4212,15 +4212,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>6</v>
       </c>
       <c r="B185" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C185" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4232,15 +4232,15 @@
         <v>35</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>6</v>
       </c>
       <c r="B186" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C186" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -4252,15 +4252,15 @@
         <v>66</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>6</v>
       </c>
       <c r="B187" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C187" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4272,15 +4272,15 @@
         <v>99</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>6</v>
       </c>
       <c r="B188" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C188" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -4292,15 +4292,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>6</v>
       </c>
       <c r="B189" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C189" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -4312,15 +4312,15 @@
         <v>163</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>6</v>
       </c>
       <c r="B190" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C190" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -4332,7 +4332,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>6</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>6</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>6</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>6</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>6</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>6</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>6</v>
       </c>
@@ -4472,15 +4472,15 @@
         <v>201</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>6</v>
       </c>
       <c r="B198" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C198" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D198">
         <v>0</v>
@@ -4492,15 +4492,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>6</v>
       </c>
       <c r="B199" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C199" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D199">
         <v>0</v>
@@ -4512,15 +4512,15 @@
         <v>46</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>6</v>
       </c>
       <c r="B200" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C200" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D200">
         <v>0</v>
@@ -4532,7 +4532,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>6</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>6</v>
       </c>
@@ -4572,47 +4572,47 @@
         <v>142</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>6</v>
       </c>
       <c r="B203" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C203" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D203">
         <v>0</v>
       </c>
       <c r="E203">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F203">
         <v>174</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>6</v>
       </c>
       <c r="B204" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C204" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D204">
         <v>0</v>
       </c>
       <c r="E204">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F204">
         <v>206</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>6</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>6</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>6</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>6</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>6</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>6</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>6</v>
       </c>
@@ -4752,15 +4752,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>6</v>
       </c>
       <c r="B212" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C212" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D212">
         <v>2</v>
@@ -4772,15 +4772,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>6</v>
       </c>
       <c r="B213" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C213" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D213">
         <v>2</v>
@@ -4792,15 +4792,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>6</v>
       </c>
       <c r="B214" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C214" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D214">
         <v>2</v>
@@ -4812,15 +4812,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>6</v>
       </c>
       <c r="B215" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C215" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D215">
         <v>2</v>
@@ -4832,15 +4832,15 @@
         <v>112</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>6</v>
       </c>
       <c r="B216" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C216" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D216">
         <v>2</v>
@@ -4852,15 +4852,15 @@
         <v>144</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>6</v>
       </c>
       <c r="B217" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C217" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D217">
         <v>2</v>
@@ -4872,15 +4872,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>6</v>
       </c>
       <c r="B218" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C218" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D218">
         <v>2</v>
@@ -4892,7 +4892,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>6</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>6</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>6</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>6</v>
       </c>
@@ -4966,13 +4966,13 @@
         <v>0</v>
       </c>
       <c r="E222">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F222">
         <v>100</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>6</v>
       </c>
@@ -4986,18 +4986,18 @@
         <v>0</v>
       </c>
       <c r="E223">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F223">
         <v>132</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>6</v>
       </c>
       <c r="B224" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C224" t="s">
         <v>18</v>
@@ -5006,41 +5006,41 @@
         <v>0</v>
       </c>
       <c r="E224">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F224">
         <v>164</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>6</v>
       </c>
       <c r="B225" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C225" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D225">
         <v>0</v>
       </c>
       <c r="E225">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F225">
         <v>196</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>6</v>
       </c>
       <c r="B226" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C226" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D226">
         <v>1</v>
@@ -5052,15 +5052,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>6</v>
       </c>
       <c r="B227" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C227" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D227">
         <v>1</v>
@@ -5072,15 +5072,15 @@
         <v>55</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>6</v>
       </c>
       <c r="B228" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C228" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D228">
         <v>1</v>
@@ -5092,15 +5092,15 @@
         <v>87</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>6</v>
       </c>
       <c r="B229" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C229" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D229">
         <v>1</v>
@@ -5112,15 +5112,15 @@
         <v>119</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>6</v>
       </c>
       <c r="B230" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C230" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -5132,15 +5132,15 @@
         <v>151</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>6</v>
       </c>
       <c r="B231" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C231" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D231">
         <v>1</v>
@@ -5152,15 +5152,15 @@
         <v>183</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>6</v>
       </c>
       <c r="B232" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C232" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -5172,15 +5172,15 @@
         <v>215</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>6</v>
       </c>
       <c r="B233" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C233" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D233">
         <v>2</v>
@@ -5192,15 +5192,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>6</v>
       </c>
       <c r="B234" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C234" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D234">
         <v>2</v>
@@ -5212,15 +5212,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>6</v>
       </c>
       <c r="B235" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C235" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D235">
         <v>2</v>
@@ -5232,15 +5232,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>6</v>
       </c>
       <c r="B236" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C236" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D236">
         <v>2</v>
@@ -5252,15 +5252,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>6</v>
       </c>
       <c r="B237" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C237" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D237">
         <v>2</v>
@@ -5272,15 +5272,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>6</v>
       </c>
       <c r="B238" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C238" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D238">
         <v>2</v>
@@ -5292,15 +5292,15 @@
         <v>178</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>6</v>
       </c>
       <c r="B239" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C239" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D239">
         <v>2</v>
@@ -5312,7 +5312,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>6</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>6</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>6</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>34</v>
       </c>
       <c r="C242" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D242">
         <v>0</v>
@@ -5372,12 +5372,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>6</v>
       </c>
       <c r="B243" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C243" t="s">
         <v>18</v>
@@ -5392,7 +5392,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>6</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>6</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>6</v>
       </c>
@@ -5446,13 +5446,13 @@
         <v>0</v>
       </c>
       <c r="E246">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F246">
         <v>218</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>6</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>33</v>
       </c>
       <c r="C247" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D247">
         <v>1</v>
@@ -5472,7 +5472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>6</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>6</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>6</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>6</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>6</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>6</v>
       </c>
@@ -5592,15 +5592,15 @@
         <v>201</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>6</v>
       </c>
       <c r="B254" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C254" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D254">
         <v>2</v>
@@ -5612,15 +5612,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>6</v>
       </c>
       <c r="B255" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C255" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D255">
         <v>2</v>
@@ -5632,15 +5632,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>6</v>
       </c>
       <c r="B256" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C256" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D256">
         <v>2</v>
@@ -5652,15 +5652,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>6</v>
       </c>
       <c r="B257" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C257" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D257">
         <v>2</v>
@@ -5672,15 +5672,15 @@
         <v>107</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>6</v>
       </c>
       <c r="B258" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C258" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D258">
         <v>2</v>
@@ -5692,15 +5692,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>6</v>
       </c>
       <c r="B259" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C259" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D259">
         <v>2</v>
@@ -5712,15 +5712,15 @@
         <v>171</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>6</v>
       </c>
       <c r="B260" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C260" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D260">
         <v>2</v>
@@ -5732,15 +5732,15 @@
         <v>203</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>6</v>
       </c>
       <c r="B261" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C261" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D261">
         <v>0</v>
@@ -5752,15 +5752,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>6</v>
       </c>
       <c r="B262" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C262" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -5772,12 +5772,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>6</v>
       </c>
       <c r="B263" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C263" t="s">
         <v>35</v>
@@ -5792,15 +5792,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>6</v>
       </c>
       <c r="B264" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C264" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -5812,15 +5812,15 @@
         <v>124</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>6</v>
       </c>
       <c r="B265" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C265" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D265">
         <v>0</v>
@@ -5832,7 +5832,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>6</v>
       </c>
@@ -5852,35 +5852,35 @@
         <v>188</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>6</v>
       </c>
       <c r="B267" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C267" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D267">
         <v>0</v>
       </c>
       <c r="E267">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F267">
         <v>220</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>6</v>
       </c>
       <c r="B268" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C268" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -5892,15 +5892,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>6</v>
       </c>
       <c r="B269" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C269" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D269">
         <v>1</v>
@@ -5912,15 +5912,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>6</v>
       </c>
       <c r="B270" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C270" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -5932,15 +5932,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>6</v>
       </c>
       <c r="B271" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C271" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D271">
         <v>1</v>
@@ -5952,12 +5952,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>6</v>
       </c>
       <c r="B272" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C272" t="s">
         <v>38</v>
@@ -5972,15 +5972,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>6</v>
       </c>
       <c r="B273" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C273" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D273">
         <v>1</v>
@@ -5992,15 +5992,15 @@
         <v>182</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>6</v>
       </c>
       <c r="B274" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C274" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D274">
         <v>1</v>
@@ -6012,15 +6012,15 @@
         <v>213</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>6</v>
       </c>
       <c r="B275" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C275" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D275">
         <v>2</v>
@@ -6032,15 +6032,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>6</v>
       </c>
       <c r="B276" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C276" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D276">
         <v>2</v>
@@ -6052,15 +6052,15 @@
         <v>57</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>6</v>
       </c>
       <c r="B277" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C277" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D277">
         <v>2</v>
@@ -6072,15 +6072,15 @@
         <v>89</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>6</v>
       </c>
       <c r="B278" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C278" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D278">
         <v>2</v>
@@ -6092,15 +6092,15 @@
         <v>121</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>6</v>
       </c>
       <c r="B279" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C279" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D279">
         <v>2</v>
@@ -6112,15 +6112,15 @@
         <v>153</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>6</v>
       </c>
       <c r="B280" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C280" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D280">
         <v>2</v>
@@ -6132,15 +6132,15 @@
         <v>185</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>6</v>
       </c>
       <c r="B281" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C281" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D281">
         <v>2</v>
@@ -6152,15 +6152,15 @@
         <v>217</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>6</v>
       </c>
       <c r="B282" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C282" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -6172,12 +6172,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>6</v>
       </c>
       <c r="B283" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C283" t="s">
         <v>14</v>
@@ -6192,15 +6192,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>6</v>
       </c>
       <c r="B284" t="s">
+        <v>20</v>
+      </c>
+      <c r="C284" t="s">
         <v>19</v>
-      </c>
-      <c r="C284" t="s">
-        <v>26</v>
       </c>
       <c r="D284">
         <v>0</v>
@@ -6212,15 +6212,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>6</v>
       </c>
       <c r="B285" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C285" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D285">
         <v>0</v>
@@ -6232,12 +6232,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>6</v>
       </c>
       <c r="B286" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C286" t="s">
         <v>31</v>
@@ -6252,7 +6252,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>6</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>6</v>
       </c>
@@ -6286,21 +6286,21 @@
         <v>0</v>
       </c>
       <c r="E288">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F288">
         <v>216</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>6</v>
       </c>
       <c r="B289" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C289" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D289">
         <v>1</v>
@@ -6312,15 +6312,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>6</v>
       </c>
       <c r="B290" t="s">
+        <v>20</v>
+      </c>
+      <c r="C290" t="s">
         <v>19</v>
-      </c>
-      <c r="C290" t="s">
-        <v>26</v>
       </c>
       <c r="D290">
         <v>1</v>
@@ -6332,15 +6332,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>6</v>
       </c>
       <c r="B291" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C291" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D291">
         <v>1</v>
@@ -6352,15 +6352,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>6</v>
       </c>
       <c r="B292" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C292" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D292">
         <v>1</v>
@@ -6372,15 +6372,15 @@
         <v>120</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>6</v>
       </c>
       <c r="B293" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C293" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D293">
         <v>1</v>
@@ -6392,15 +6392,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>6</v>
       </c>
       <c r="B294" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C294" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D294">
         <v>1</v>
@@ -6412,15 +6412,15 @@
         <v>184</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>6</v>
       </c>
       <c r="B295" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C295" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D295">
         <v>1</v>
@@ -6432,7 +6432,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>6</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>6</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>6</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>6</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>6</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>6</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>6</v>
       </c>
@@ -6572,15 +6572,15 @@
         <v>218</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>6</v>
       </c>
       <c r="B303" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C303" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D303">
         <v>0</v>
@@ -6592,7 +6592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>6</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>6</v>
       </c>
@@ -6620,7 +6620,7 @@
         <v>31</v>
       </c>
       <c r="C305" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -6632,7 +6632,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>6</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>6</v>
       </c>
@@ -6666,13 +6666,13 @@
         <v>0</v>
       </c>
       <c r="E307">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F307">
         <v>140</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>6</v>
       </c>
@@ -6686,13 +6686,13 @@
         <v>0</v>
       </c>
       <c r="E308">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F308">
         <v>172</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>6</v>
       </c>
@@ -6706,13 +6706,13 @@
         <v>0</v>
       </c>
       <c r="E309">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F309">
         <v>204</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>6</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>6</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>6</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>6</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>6</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>6</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>6</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>6</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>6</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>6</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>6</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>6</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>6</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>6</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>6</v>
       </c>
@@ -7012,12 +7012,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>6</v>
       </c>
       <c r="B325" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C325" t="s">
         <v>7</v>
@@ -7032,7 +7032,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>6</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>6</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>6</v>
       </c>
@@ -7086,13 +7086,13 @@
         <v>0</v>
       </c>
       <c r="E328">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F328">
         <v>135</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>6</v>
       </c>
@@ -7106,18 +7106,18 @@
         <v>0</v>
       </c>
       <c r="E329">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F329">
         <v>167</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>6</v>
       </c>
       <c r="B330" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C330" t="s">
         <v>10</v>
@@ -7126,21 +7126,21 @@
         <v>0</v>
       </c>
       <c r="E330">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F330">
         <v>199</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>6</v>
       </c>
       <c r="B331" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C331" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D331">
         <v>1</v>
@@ -7152,15 +7152,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>6</v>
       </c>
       <c r="B332" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C332" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D332">
         <v>1</v>
@@ -7172,15 +7172,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>6</v>
       </c>
       <c r="B333" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C333" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D333">
         <v>1</v>
@@ -7192,15 +7192,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>6</v>
       </c>
       <c r="B334" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C334" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D334">
         <v>1</v>
@@ -7212,15 +7212,15 @@
         <v>125</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>6</v>
       </c>
       <c r="B335" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C335" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D335">
         <v>1</v>
@@ -7232,15 +7232,15 @@
         <v>157</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>6</v>
       </c>
       <c r="B336" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C336" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D336">
         <v>1</v>
@@ -7252,15 +7252,15 @@
         <v>189</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>6</v>
       </c>
       <c r="B337" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C337" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D337">
         <v>1</v>
@@ -7272,15 +7272,15 @@
         <v>221</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>6</v>
       </c>
       <c r="B338" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C338" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D338">
         <v>2</v>
@@ -7292,15 +7292,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>6</v>
       </c>
       <c r="B339" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C339" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D339">
         <v>2</v>
@@ -7312,15 +7312,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>6</v>
       </c>
       <c r="B340" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C340" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D340">
         <v>2</v>
@@ -7332,15 +7332,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>6</v>
       </c>
       <c r="B341" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C341" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D341">
         <v>2</v>
@@ -7352,15 +7352,15 @@
         <v>116</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>6</v>
       </c>
       <c r="B342" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C342" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D342">
         <v>2</v>
@@ -7372,15 +7372,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>6</v>
       </c>
       <c r="B343" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C343" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D343">
         <v>2</v>
@@ -7392,15 +7392,15 @@
         <v>180</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>6</v>
       </c>
       <c r="B344" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C344" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D344">
         <v>2</v>
@@ -7412,7 +7412,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>6</v>
       </c>
@@ -7432,15 +7432,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>6</v>
       </c>
       <c r="B346" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C346" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D346">
         <v>0</v>
@@ -7452,7 +7452,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>6</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>6</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>9</v>
       </c>
       <c r="C348" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D348">
         <v>0</v>
@@ -7492,7 +7492,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>6</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>6</v>
       </c>
@@ -7526,13 +7526,13 @@
         <v>0</v>
       </c>
       <c r="E350">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F350">
         <v>176</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>6</v>
       </c>
@@ -7546,13 +7546,13 @@
         <v>0</v>
       </c>
       <c r="E351">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F351">
         <v>208</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>6</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>6</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>6</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>6</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>6</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>6</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>6</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>6</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>6</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>6</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>6</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>6</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>6</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>6</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>6</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>6</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>6</v>
       </c>
@@ -7880,7 +7880,7 @@
         <v>38</v>
       </c>
       <c r="C368" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D368">
         <v>0</v>
@@ -7892,7 +7892,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>6</v>
       </c>
@@ -7906,13 +7906,13 @@
         <v>0</v>
       </c>
       <c r="E369">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F369">
         <v>101</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>6</v>
       </c>
@@ -7926,33 +7926,33 @@
         <v>0</v>
       </c>
       <c r="E370">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F370">
         <v>133</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>6</v>
       </c>
       <c r="B371" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C371" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D371">
         <v>0</v>
       </c>
       <c r="E371">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F371">
         <v>165</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>6</v>
       </c>
@@ -7960,19 +7960,19 @@
         <v>7</v>
       </c>
       <c r="C372" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D372">
         <v>0</v>
       </c>
       <c r="E372">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F372">
         <v>197</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>6</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>6</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>6</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>6</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>6</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>6</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>6</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>6</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>6</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>6</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>6</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>6</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>6</v>
       </c>
@@ -8232,7 +8232,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>6</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>6</v>
       </c>
@@ -8272,15 +8272,15 @@
         <v>18</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>6</v>
       </c>
       <c r="B388" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C388" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D388">
         <v>0</v>
@@ -8292,7 +8292,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>6</v>
       </c>
@@ -8312,15 +8312,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>6</v>
       </c>
       <c r="B390" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C390" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D390">
         <v>0</v>
@@ -8332,7 +8332,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>6</v>
       </c>
@@ -8352,15 +8352,15 @@
         <v>146</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>6</v>
       </c>
       <c r="B392" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C392" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D392">
         <v>0</v>
@@ -8372,7 +8372,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>6</v>
       </c>
@@ -8386,13 +8386,13 @@
         <v>0</v>
       </c>
       <c r="E393">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F393">
         <v>210</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>6</v>
       </c>
@@ -8412,7 +8412,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>6</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>6</v>
       </c>
@@ -8452,7 +8452,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>6</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>6</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>6</v>
       </c>
@@ -8512,7 +8512,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>6</v>
       </c>
@@ -8532,15 +8532,15 @@
         <v>205</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>6</v>
       </c>
       <c r="B401" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C401" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D401">
         <v>2</v>
@@ -8552,15 +8552,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>6</v>
       </c>
       <c r="B402" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C402" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D402">
         <v>2</v>
@@ -8572,15 +8572,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>6</v>
       </c>
       <c r="B403" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C403" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D403">
         <v>2</v>
@@ -8592,15 +8592,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>6</v>
       </c>
       <c r="B404" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C404" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D404">
         <v>2</v>
@@ -8612,15 +8612,15 @@
         <v>127</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>6</v>
       </c>
       <c r="B405" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C405" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D405">
         <v>2</v>
@@ -8632,15 +8632,15 @@
         <v>159</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>6</v>
       </c>
       <c r="B406" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C406" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D406">
         <v>2</v>
@@ -8652,15 +8652,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>6</v>
       </c>
       <c r="B407" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C407" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D407">
         <v>2</v>
@@ -8672,7 +8672,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>6</v>
       </c>
@@ -8692,7 +8692,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>6</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>6</v>
       </c>
@@ -8732,15 +8732,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>6</v>
       </c>
       <c r="B411" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C411" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D411">
         <v>0</v>
@@ -8752,7 +8752,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>6</v>
       </c>
@@ -8766,13 +8766,13 @@
         <v>0</v>
       </c>
       <c r="E412">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F412">
         <v>134</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>6</v>
       </c>
@@ -8786,18 +8786,18 @@
         <v>0</v>
       </c>
       <c r="E413">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F413">
         <v>166</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>6</v>
       </c>
       <c r="B414" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C414" t="s">
         <v>9</v>
@@ -8806,13 +8806,13 @@
         <v>0</v>
       </c>
       <c r="E414">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F414">
         <v>198</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>6</v>
       </c>
@@ -8832,7 +8832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>6</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>6</v>
       </c>
@@ -8872,7 +8872,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>6</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>6</v>
       </c>
@@ -8912,7 +8912,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>6</v>
       </c>
@@ -8932,7 +8932,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>6</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>6</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>6</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>6</v>
       </c>
@@ -9012,7 +9012,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>6</v>
       </c>
@@ -9032,7 +9032,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>6</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>6</v>
       </c>
@@ -9072,7 +9072,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>6</v>
       </c>
@@ -9092,7 +9092,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>6</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>31</v>
       </c>
       <c r="C429" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D429">
         <v>0</v>
@@ -9112,15 +9112,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>6</v>
       </c>
       <c r="B430" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C430" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D430">
         <v>0</v>
@@ -9132,7 +9132,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>6</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>6</v>
       </c>
@@ -9172,7 +9172,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>6</v>
       </c>
@@ -9186,13 +9186,13 @@
         <v>0</v>
       </c>
       <c r="E433">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F433">
         <v>139</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>6</v>
       </c>
@@ -9206,13 +9206,13 @@
         <v>0</v>
       </c>
       <c r="E434">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F434">
         <v>171</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>6</v>
       </c>
@@ -9226,21 +9226,21 @@
         <v>0</v>
       </c>
       <c r="E435">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F435">
         <v>203</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>6</v>
       </c>
       <c r="B436" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C436" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D436">
         <v>1</v>
@@ -9252,15 +9252,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>6</v>
       </c>
       <c r="B437" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C437" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D437">
         <v>1</v>
@@ -9272,15 +9272,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>6</v>
       </c>
       <c r="B438" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C438" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D438">
         <v>1</v>
@@ -9292,15 +9292,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>6</v>
       </c>
       <c r="B439" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C439" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D439">
         <v>1</v>
@@ -9312,15 +9312,15 @@
         <v>111</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>6</v>
       </c>
       <c r="B440" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C440" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D440">
         <v>1</v>
@@ -9332,15 +9332,15 @@
         <v>142</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>6</v>
       </c>
       <c r="B441" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C441" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D441">
         <v>1</v>
@@ -9352,15 +9352,15 @@
         <v>175</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>6</v>
       </c>
       <c r="B442" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C442" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D442">
         <v>1</v>
@@ -9372,7 +9372,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>6</v>
       </c>
@@ -9392,7 +9392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>6</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>6</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>6</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>6</v>
       </c>
@@ -9472,7 +9472,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>6</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>6</v>
       </c>
@@ -9512,15 +9512,15 @@
         <v>193</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>6</v>
       </c>
       <c r="B450" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C450" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D450">
         <v>0</v>
@@ -9532,7 +9532,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>6</v>
       </c>
@@ -9552,12 +9552,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>6</v>
       </c>
       <c r="B452" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C452" t="s">
         <v>38</v>
@@ -9572,7 +9572,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>6</v>
       </c>
@@ -9586,81 +9586,81 @@
         <v>0</v>
       </c>
       <c r="E453">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F453">
         <v>98</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>6</v>
       </c>
       <c r="B454" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C454" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D454">
         <v>0</v>
       </c>
       <c r="E454">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F454">
         <v>130</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>6</v>
       </c>
       <c r="B455" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C455" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D455">
         <v>0</v>
       </c>
       <c r="E455">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F455">
         <v>162</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>6</v>
       </c>
       <c r="B456" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C456" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D456">
         <v>0</v>
       </c>
       <c r="E456">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F456">
         <v>194</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>6</v>
       </c>
       <c r="B457" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C457" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D457">
         <v>1</v>
@@ -9672,15 +9672,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>6</v>
       </c>
       <c r="B458" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C458" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D458">
         <v>1</v>
@@ -9692,15 +9692,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>6</v>
       </c>
       <c r="B459" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C459" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D459">
         <v>1</v>
@@ -9712,15 +9712,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>6</v>
       </c>
       <c r="B460" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C460" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D460">
         <v>1</v>
@@ -9732,15 +9732,15 @@
         <v>124</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>6</v>
       </c>
       <c r="B461" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C461" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D461">
         <v>1</v>
@@ -9752,15 +9752,15 @@
         <v>156</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>6</v>
       </c>
       <c r="B462" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C462" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D462">
         <v>1</v>
@@ -9772,15 +9772,15 @@
         <v>188</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>6</v>
       </c>
       <c r="B463" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C463" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D463">
         <v>1</v>
@@ -9792,15 +9792,15 @@
         <v>220</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>6</v>
       </c>
       <c r="B464" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C464" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D464">
         <v>2</v>
@@ -9812,15 +9812,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>6</v>
       </c>
       <c r="B465" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C465" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D465">
         <v>2</v>
@@ -9832,15 +9832,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>6</v>
       </c>
       <c r="B466" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C466" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D466">
         <v>2</v>
@@ -9852,15 +9852,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>6</v>
       </c>
       <c r="B467" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C467" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D467">
         <v>2</v>
@@ -9872,15 +9872,15 @@
         <v>125</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>6</v>
       </c>
       <c r="B468" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C468" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D468">
         <v>2</v>
@@ -9892,15 +9892,15 @@
         <v>157</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>6</v>
       </c>
       <c r="B469" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C469" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D469">
         <v>2</v>
@@ -9912,15 +9912,15 @@
         <v>189</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>6</v>
       </c>
       <c r="B470" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C470" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D470">
         <v>2</v>
@@ -9932,7 +9932,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>6</v>
       </c>
@@ -9952,15 +9952,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>6</v>
       </c>
       <c r="B472" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C472" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D472">
         <v>0</v>
@@ -9972,7 +9972,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>6</v>
       </c>
@@ -9992,7 +9992,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>6</v>
       </c>
@@ -10006,53 +10006,53 @@
         <v>0</v>
       </c>
       <c r="E474">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F474">
         <v>99</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>6</v>
       </c>
       <c r="B475" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C475" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D475">
         <v>0</v>
       </c>
       <c r="E475">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F475">
         <v>131</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>6</v>
       </c>
       <c r="B476" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C476" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D476">
         <v>0</v>
       </c>
       <c r="E476">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F476">
         <v>163</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>6</v>
       </c>
@@ -10066,21 +10066,21 @@
         <v>0</v>
       </c>
       <c r="E477">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F477">
         <v>195</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>6</v>
       </c>
       <c r="B478" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C478" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D478">
         <v>1</v>
@@ -10092,15 +10092,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>6</v>
       </c>
       <c r="B479" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C479" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D479">
         <v>1</v>
@@ -10112,12 +10112,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>6</v>
       </c>
       <c r="B480" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C480" t="s">
         <v>33</v>
@@ -10132,12 +10132,12 @@
         <v>84</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>6</v>
       </c>
       <c r="B481" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C481" t="s">
         <v>35</v>
@@ -10152,15 +10152,15 @@
         <v>118</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>6</v>
       </c>
       <c r="B482" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C482" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D482">
         <v>1</v>
@@ -10172,12 +10172,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>6</v>
       </c>
       <c r="B483" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C483" t="s">
         <v>9</v>
@@ -10192,15 +10192,15 @@
         <v>180</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>6</v>
       </c>
       <c r="B484" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C484" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D484">
         <v>1</v>
@@ -10212,15 +10212,15 @@
         <v>214</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>6</v>
       </c>
       <c r="B485" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C485" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D485">
         <v>2</v>
@@ -10232,15 +10232,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>6</v>
       </c>
       <c r="B486" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C486" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D486">
         <v>2</v>
@@ -10252,15 +10252,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>6</v>
       </c>
       <c r="B487" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C487" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D487">
         <v>2</v>
@@ -10272,15 +10272,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>6</v>
       </c>
       <c r="B488" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C488" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D488">
         <v>2</v>
@@ -10292,15 +10292,15 @@
         <v>109</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>6</v>
       </c>
       <c r="B489" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C489" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D489">
         <v>2</v>
@@ -10312,15 +10312,15 @@
         <v>141</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>6</v>
       </c>
       <c r="B490" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C490" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D490">
         <v>2</v>
@@ -10332,15 +10332,15 @@
         <v>173</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>6</v>
       </c>
       <c r="B491" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C491" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D491">
         <v>2</v>
@@ -10352,7 +10352,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>6</v>
       </c>
@@ -10372,7 +10372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>6</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>6</v>
       </c>
@@ -10412,15 +10412,15 @@
         <v>73</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>6</v>
       </c>
       <c r="B495" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C495" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D495">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>6</v>
       </c>
@@ -10446,38 +10446,38 @@
         <v>0</v>
       </c>
       <c r="E496">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F496">
         <v>137</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>6</v>
       </c>
       <c r="B497" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C497" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D497">
         <v>0</v>
       </c>
       <c r="E497">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F497">
         <v>169</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>6</v>
       </c>
       <c r="B498" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C498" t="s">
         <v>36</v>
@@ -10486,13 +10486,13 @@
         <v>0</v>
       </c>
       <c r="E498">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F498">
         <v>201</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>6</v>
       </c>
@@ -10512,7 +10512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>6</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>6</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>6</v>
       </c>
@@ -10560,7 +10560,7 @@
         <v>38</v>
       </c>
       <c r="C502" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D502">
         <v>1</v>
@@ -10572,7 +10572,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>6</v>
       </c>
@@ -10592,7 +10592,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>6</v>
       </c>
@@ -10612,7 +10612,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>6</v>
       </c>
@@ -10632,15 +10632,15 @@
         <v>196</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>6</v>
       </c>
       <c r="B506" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C506" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D506">
         <v>2</v>
@@ -10652,15 +10652,15 @@
         <v>4</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>6</v>
       </c>
       <c r="B507" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C507" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D507">
         <v>2</v>
@@ -10672,15 +10672,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>6</v>
       </c>
       <c r="B508" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C508" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D508">
         <v>2</v>
@@ -10692,15 +10692,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>6</v>
       </c>
       <c r="B509" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C509" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D509">
         <v>2</v>
@@ -10712,15 +10712,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>6</v>
       </c>
       <c r="B510" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C510" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D510">
         <v>2</v>
@@ -10732,15 +10732,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>6</v>
       </c>
       <c r="B511" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C511" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D511">
         <v>2</v>
@@ -10752,15 +10752,15 @@
         <v>164</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>6</v>
       </c>
       <c r="B512" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C512" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D512">
         <v>2</v>
@@ -10772,7 +10772,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>6</v>
       </c>
@@ -10792,7 +10792,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>6</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>6</v>
       </c>
@@ -10832,7 +10832,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>6</v>
       </c>
@@ -10852,7 +10852,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>6</v>
       </c>
@@ -10872,15 +10872,15 @@
         <v>153</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>6</v>
       </c>
       <c r="B518" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C518" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D518">
         <v>0</v>
@@ -10892,27 +10892,27 @@
         <v>185</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>6</v>
       </c>
       <c r="B519" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C519" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D519">
         <v>0</v>
       </c>
       <c r="E519">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F519">
         <v>217</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>6</v>
       </c>
@@ -10932,7 +10932,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>6</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>6</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>6</v>
       </c>
@@ -10992,7 +10992,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>6</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>6</v>
       </c>
@@ -11032,7 +11032,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>6</v>
       </c>
@@ -11052,7 +11052,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>6</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>6</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>6</v>
       </c>
@@ -11112,7 +11112,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>6</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>6</v>
       </c>
@@ -11152,7 +11152,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>6</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>6</v>
       </c>
@@ -11192,15 +11192,15 @@
         <v>207</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>6</v>
       </c>
       <c r="B534" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C534" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D534">
         <v>0</v>
@@ -11212,15 +11212,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>6</v>
       </c>
       <c r="B535" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C535" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D535">
         <v>0</v>
@@ -11232,12 +11232,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>6</v>
       </c>
       <c r="B536" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C536" t="s">
         <v>33</v>
@@ -11252,7 +11252,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>6</v>
       </c>
@@ -11266,13 +11266,13 @@
         <v>0</v>
       </c>
       <c r="E537">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F537">
         <v>96</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>6</v>
       </c>
@@ -11286,53 +11286,53 @@
         <v>0</v>
       </c>
       <c r="E538">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F538">
         <v>128</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>6</v>
       </c>
       <c r="B539" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C539" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D539">
         <v>0</v>
       </c>
       <c r="E539">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F539">
         <v>160</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>6</v>
       </c>
       <c r="B540" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C540" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D540">
         <v>0</v>
       </c>
       <c r="E540">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F540">
         <v>192</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>6</v>
       </c>
@@ -11352,7 +11352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>6</v>
       </c>
@@ -11372,7 +11372,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>6</v>
       </c>
@@ -11392,7 +11392,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>6</v>
       </c>
@@ -11412,7 +11412,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>6</v>
       </c>
@@ -11432,7 +11432,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>6</v>
       </c>
@@ -11452,7 +11452,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>6</v>
       </c>
@@ -11472,15 +11472,15 @@
         <v>217</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>6</v>
       </c>
       <c r="B548" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C548" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D548">
         <v>2</v>
@@ -11492,15 +11492,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>6</v>
       </c>
       <c r="B549" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C549" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D549">
         <v>2</v>
@@ -11512,15 +11512,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>6</v>
       </c>
       <c r="B550" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C550" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D550">
         <v>2</v>
@@ -11532,15 +11532,15 @@
         <v>66</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>6</v>
       </c>
       <c r="B551" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C551" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D551">
         <v>2</v>
@@ -11552,15 +11552,15 @@
         <v>98</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>6</v>
       </c>
       <c r="B552" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C552" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D552">
         <v>2</v>
@@ -11572,15 +11572,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>6</v>
       </c>
       <c r="B553" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C553" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D553">
         <v>2</v>
@@ -11592,15 +11592,15 @@
         <v>162</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>6</v>
       </c>
       <c r="B554" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C554" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D554">
         <v>2</v>
@@ -11612,15 +11612,15 @@
         <v>194</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>6</v>
       </c>
       <c r="B555" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C555" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D555">
         <v>0</v>
@@ -11632,15 +11632,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>6</v>
       </c>
       <c r="B556" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C556" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D556">
         <v>0</v>
@@ -11652,15 +11652,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>6</v>
       </c>
       <c r="B557" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C557" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D557">
         <v>0</v>
@@ -11672,15 +11672,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>6</v>
       </c>
       <c r="B558" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C558" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D558">
         <v>0</v>
@@ -11692,15 +11692,15 @@
         <v>117</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>6</v>
       </c>
       <c r="B559" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C559" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D559">
         <v>0</v>
@@ -11712,12 +11712,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>6</v>
       </c>
       <c r="B560" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C560" t="s">
         <v>31</v>
@@ -11732,7 +11732,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>6</v>
       </c>
@@ -11746,21 +11746,21 @@
         <v>0</v>
       </c>
       <c r="E561">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F561">
         <v>213</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>6</v>
       </c>
       <c r="B562" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C562" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D562">
         <v>1</v>
@@ -11772,15 +11772,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>6</v>
       </c>
       <c r="B563" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C563" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D563">
         <v>1</v>
@@ -11792,15 +11792,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>6</v>
       </c>
       <c r="B564" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C564" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D564">
         <v>1</v>
@@ -11812,15 +11812,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>6</v>
       </c>
       <c r="B565" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C565" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D565">
         <v>1</v>
@@ -11832,15 +11832,15 @@
         <v>116</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>6</v>
       </c>
       <c r="B566" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C566" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D566">
         <v>1</v>
@@ -11852,15 +11852,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>6</v>
       </c>
       <c r="B567" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C567" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D567">
         <v>1</v>
@@ -11872,15 +11872,15 @@
         <v>181</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>6</v>
       </c>
       <c r="B568" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C568" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D568">
         <v>1</v>
@@ -11892,7 +11892,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>6</v>
       </c>
@@ -11912,7 +11912,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>6</v>
       </c>
@@ -11932,7 +11932,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>6</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>6</v>
       </c>
@@ -11972,7 +11972,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>6</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>6</v>
       </c>
@@ -12012,7 +12012,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>6</v>
       </c>
@@ -12032,15 +12032,15 @@
         <v>219</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>6</v>
       </c>
       <c r="B576" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C576" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D576">
         <v>0</v>
@@ -12052,7 +12052,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>6</v>
       </c>
@@ -12072,15 +12072,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>6</v>
       </c>
       <c r="B578" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C578" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D578">
         <v>0</v>
@@ -12092,7 +12092,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>6</v>
       </c>
@@ -12112,7 +12112,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>6</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>6</v>
       </c>
@@ -12152,7 +12152,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>6</v>
       </c>
@@ -12166,13 +12166,13 @@
         <v>0</v>
       </c>
       <c r="E582">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F582">
         <v>211</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>6</v>
       </c>
@@ -12192,7 +12192,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>6</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>6</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>6</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>6</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>6</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>6</v>
       </c>
@@ -12312,15 +12312,15 @@
         <v>223</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>6</v>
       </c>
       <c r="B590" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C590" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D590">
         <v>2</v>
@@ -12332,15 +12332,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>6</v>
       </c>
       <c r="B591" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C591" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D591">
         <v>2</v>
@@ -12352,15 +12352,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>6</v>
       </c>
       <c r="B592" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C592" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D592">
         <v>2</v>
@@ -12372,15 +12372,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>6</v>
       </c>
       <c r="B593" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C593" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D593">
         <v>2</v>
@@ -12392,15 +12392,15 @@
         <v>103</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>6</v>
       </c>
       <c r="B594" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C594" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D594">
         <v>2</v>
@@ -12412,15 +12412,15 @@
         <v>135</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>6</v>
       </c>
       <c r="B595" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C595" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D595">
         <v>2</v>
@@ -12432,15 +12432,15 @@
         <v>167</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>6</v>
       </c>
       <c r="B596" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C596" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D596">
         <v>2</v>
@@ -12452,7 +12452,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>6</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>6</v>
       </c>
@@ -12480,7 +12480,7 @@
         <v>33</v>
       </c>
       <c r="C598" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D598">
         <v>0</v>
@@ -12492,15 +12492,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>6</v>
       </c>
       <c r="B599" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C599" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D599">
         <v>0</v>
@@ -12512,7 +12512,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>6</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>6</v>
       </c>
@@ -12546,61 +12546,61 @@
         <v>0</v>
       </c>
       <c r="E601">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F601">
         <v>138</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>6</v>
       </c>
       <c r="B602" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C602" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D602">
         <v>0</v>
       </c>
       <c r="E602">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F602">
         <v>170</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>6</v>
       </c>
       <c r="B603" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C603" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D603">
         <v>0</v>
       </c>
       <c r="E603">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F603">
         <v>202</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>6</v>
       </c>
       <c r="B604" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C604" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D604">
         <v>1</v>
@@ -12612,15 +12612,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>6</v>
       </c>
       <c r="B605" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C605" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D605">
         <v>1</v>
@@ -12632,15 +12632,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>6</v>
       </c>
       <c r="B606" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C606" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D606">
         <v>1</v>
@@ -12652,15 +12652,15 @@
         <v>81</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>6</v>
       </c>
       <c r="B607" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C607" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D607">
         <v>1</v>
@@ -12672,15 +12672,15 @@
         <v>112</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>6</v>
       </c>
       <c r="B608" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C608" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D608">
         <v>1</v>
@@ -12692,15 +12692,15 @@
         <v>145</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>6</v>
       </c>
       <c r="B609" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C609" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D609">
         <v>1</v>
@@ -12712,15 +12712,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>6</v>
       </c>
       <c r="B610" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C610" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D610">
         <v>1</v>
@@ -12732,15 +12732,15 @@
         <v>209</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>6</v>
       </c>
       <c r="B611" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C611" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D611">
         <v>2</v>
@@ -12752,15 +12752,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>6</v>
       </c>
       <c r="B612" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C612" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D612">
         <v>2</v>
@@ -12772,15 +12772,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>6</v>
       </c>
       <c r="B613" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C613" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D613">
         <v>2</v>
@@ -12792,15 +12792,15 @@
         <v>72</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>6</v>
       </c>
       <c r="B614" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C614" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D614">
         <v>2</v>
@@ -12812,15 +12812,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>6</v>
       </c>
       <c r="B615" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C615" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D615">
         <v>2</v>
@@ -12832,15 +12832,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>6</v>
       </c>
       <c r="B616" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C616" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D616">
         <v>2</v>
@@ -12852,15 +12852,15 @@
         <v>168</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>6</v>
       </c>
       <c r="B617" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C617" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D617">
         <v>2</v>
@@ -12872,15 +12872,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>6</v>
       </c>
       <c r="B618" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C618" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D618">
         <v>0</v>
@@ -12892,15 +12892,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>6</v>
       </c>
       <c r="B619" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C619" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D619">
         <v>0</v>
@@ -12912,15 +12912,15 @@
         <v>55</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>6</v>
       </c>
       <c r="B620" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C620" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D620">
         <v>0</v>
@@ -12932,7 +12932,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>6</v>
       </c>
@@ -12952,7 +12952,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>6</v>
       </c>
@@ -12972,7 +12972,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>6</v>
       </c>
@@ -12992,27 +12992,27 @@
         <v>183</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>6</v>
       </c>
       <c r="B624" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C624" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D624">
         <v>0</v>
       </c>
       <c r="E624">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F624">
         <v>215</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>6</v>
       </c>
@@ -13032,7 +13032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>6</v>
       </c>
@@ -13052,7 +13052,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>6</v>
       </c>
@@ -13072,7 +13072,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>6</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>6</v>
       </c>
@@ -13112,7 +13112,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>6</v>
       </c>
@@ -13120,7 +13120,7 @@
         <v>35</v>
       </c>
       <c r="C630" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D630">
         <v>1</v>
@@ -13132,7 +13132,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>6</v>
       </c>
@@ -13152,7 +13152,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>6</v>
       </c>
@@ -13172,7 +13172,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>6</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>6</v>
       </c>
@@ -13212,7 +13212,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>6</v>
       </c>
@@ -13232,7 +13232,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>6</v>
       </c>
@@ -13252,7 +13252,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>6</v>
       </c>
@@ -13272,7 +13272,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>6</v>
       </c>
@@ -13292,7 +13292,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>6</v>
       </c>
@@ -13312,7 +13312,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>6</v>
       </c>
@@ -13332,7 +13332,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>6</v>
       </c>
@@ -13352,15 +13352,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>6</v>
       </c>
       <c r="B642" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C642" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D642">
         <v>0</v>
@@ -13372,15 +13372,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>6</v>
       </c>
       <c r="B643" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C643" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D643">
         <v>0</v>
@@ -13392,7 +13392,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>6</v>
       </c>
@@ -13412,27 +13412,27 @@
         <v>190</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>6</v>
       </c>
       <c r="B645" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C645" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D645">
         <v>0</v>
       </c>
       <c r="E645">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F645">
         <v>222</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>6</v>
       </c>
@@ -13452,7 +13452,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>6</v>
       </c>
@@ -13472,7 +13472,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>6</v>
       </c>
@@ -13492,7 +13492,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>6</v>
       </c>
@@ -13512,7 +13512,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>6</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>6</v>
       </c>
@@ -13552,7 +13552,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>6</v>
       </c>
@@ -13572,7 +13572,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>6</v>
       </c>
@@ -13592,7 +13592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>6</v>
       </c>
@@ -13612,7 +13612,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>6</v>
       </c>
@@ -13632,7 +13632,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>6</v>
       </c>
@@ -13652,7 +13652,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>6</v>
       </c>
@@ -13672,7 +13672,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>6</v>
       </c>
@@ -13692,7 +13692,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>6</v>
       </c>
@@ -13712,15 +13712,15 @@
         <v>209</v>
       </c>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>6</v>
       </c>
       <c r="B660" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C660" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D660">
         <v>0</v>
@@ -13732,15 +13732,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>6</v>
       </c>
       <c r="B661" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C661" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D661">
         <v>0</v>
@@ -13752,15 +13752,15 @@
         <v>52</v>
       </c>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>6</v>
       </c>
       <c r="B662" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C662" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D662">
         <v>0</v>
@@ -13772,15 +13772,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>6</v>
       </c>
       <c r="B663" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C663" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D663">
         <v>0</v>
@@ -13792,7 +13792,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>6</v>
       </c>
@@ -13812,7 +13812,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>6</v>
       </c>
@@ -13820,7 +13820,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D665">
         <v>0</v>
@@ -13832,7 +13832,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>6</v>
       </c>
@@ -13846,13 +13846,13 @@
         <v>0</v>
       </c>
       <c r="E666">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F666">
         <v>212</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>6</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>6</v>
       </c>
@@ -13892,7 +13892,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>6</v>
       </c>
@@ -13912,7 +13912,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>6</v>
       </c>
@@ -13932,7 +13932,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>6</v>
       </c>
@@ -13952,7 +13952,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>6</v>
       </c>
@@ -13972,7 +13972,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>6</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>6</v>
       </c>
       <c r="B674" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C674" t="s">
         <v>14</v>
@@ -14017,7 +14017,7 @@
         <v>6</v>
       </c>
       <c r="B675" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C675" t="s">
         <v>31</v>
@@ -14037,10 +14037,10 @@
         <v>6</v>
       </c>
       <c r="B676" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C676" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D676">
         <v>0</v>
@@ -14077,10 +14077,10 @@
         <v>6</v>
       </c>
       <c r="B678" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C678" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D678">
         <v>0</v>
@@ -14157,7 +14157,7 @@
         <v>6</v>
       </c>
       <c r="B682" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C682" t="s">
         <v>34</v>
@@ -14177,10 +14177,10 @@
         <v>6</v>
       </c>
       <c r="B683" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C683" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D683">
         <v>0</v>
@@ -14197,10 +14197,10 @@
         <v>6</v>
       </c>
       <c r="B684" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C684" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D684">
         <v>0</v>
@@ -14217,10 +14217,10 @@
         <v>6</v>
       </c>
       <c r="B685" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C685" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D685">
         <v>0</v>
@@ -14237,10 +14237,10 @@
         <v>6</v>
       </c>
       <c r="B686" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C686" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D686">
         <v>0</v>
@@ -14257,10 +14257,10 @@
         <v>6</v>
       </c>
       <c r="B687" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C687" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D687">
         <v>0</v>
@@ -14277,10 +14277,10 @@
         <v>6</v>
       </c>
       <c r="B688" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C688" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D688">
         <v>0</v>
@@ -14317,7 +14317,7 @@
         <v>6</v>
       </c>
       <c r="B690" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C690" t="s">
         <v>7</v>
@@ -14337,10 +14337,10 @@
         <v>6</v>
       </c>
       <c r="B691" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C691" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D691">
         <v>0</v>
@@ -14357,10 +14357,10 @@
         <v>6</v>
       </c>
       <c r="B692" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C692" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D692">
         <v>0</v>
@@ -14377,10 +14377,10 @@
         <v>6</v>
       </c>
       <c r="B693" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C693" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D693">
         <v>0</v>
@@ -14397,10 +14397,10 @@
         <v>6</v>
       </c>
       <c r="B694" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C694" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D694">
         <v>0</v>
@@ -14417,7 +14417,7 @@
         <v>6</v>
       </c>
       <c r="B695" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C695" t="s">
         <v>31</v>
@@ -14437,10 +14437,10 @@
         <v>6</v>
       </c>
       <c r="B696" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C696" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D696">
         <v>0</v>
@@ -14457,10 +14457,10 @@
         <v>6</v>
       </c>
       <c r="B697" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C697" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D697">
         <v>0</v>
@@ -14497,7 +14497,7 @@
         <v>6</v>
       </c>
       <c r="B699" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C699" t="s">
         <v>38</v>
@@ -14537,10 +14537,10 @@
         <v>6</v>
       </c>
       <c r="B701" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C701" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D701">
         <v>0</v>
@@ -14557,10 +14557,10 @@
         <v>6</v>
       </c>
       <c r="B702" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C702" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D702">
         <v>0</v>
@@ -14577,7 +14577,7 @@
         <v>6</v>
       </c>
       <c r="B703" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C703" t="s">
         <v>17</v>
@@ -14637,10 +14637,10 @@
         <v>6</v>
       </c>
       <c r="B706" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C706" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D706">
         <v>0</v>
